--- a/data/excel/peer_groups.xlsx
+++ b/data/excel/peer_groups.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
           <t>HDFCBANK</t>
         </is>
       </c>
-      <c r="D2" t="b">
+      <c r="D2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -470,7 +470,7 @@
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="D3" t="b">
+      <c r="D3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -488,7 +488,7 @@
           <t>AXISBANK</t>
         </is>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -506,7 +506,7 @@
           <t>KOTAKBANK</t>
         </is>
       </c>
-      <c r="D5" t="b">
+      <c r="D5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -516,16 +516,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Private Banks</t>
+          <t>Public Sector Banks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-      <c r="D6" t="b">
-        <v>0</v>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -539,11 +539,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SBIN</t>
-        </is>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -557,10 +557,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
-        </is>
-      </c>
-      <c r="D8" t="b">
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -575,10 +575,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CANBK</t>
-        </is>
-      </c>
-      <c r="D9" t="b">
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -588,16 +588,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Public Sector Banks</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="D10" t="b">
-        <v>0</v>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -611,11 +611,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TCS</t>
-        </is>
-      </c>
-      <c r="D11" t="b">
-        <v>1</v>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -629,10 +629,10 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INFY</t>
-        </is>
-      </c>
-      <c r="D12" t="b">
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -647,10 +647,10 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
-        </is>
-      </c>
-      <c r="D13" t="b">
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -660,16 +660,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="D14" t="b">
-        <v>0</v>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -678,15 +678,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LTIM</t>
-        </is>
-      </c>
-      <c r="D15" t="b">
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -701,11 +701,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
-        </is>
-      </c>
-      <c r="D16" t="b">
-        <v>1</v>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -719,10 +719,10 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CIPLA</t>
-        </is>
-      </c>
-      <c r="D17" t="b">
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -737,10 +737,10 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
-        </is>
-      </c>
-      <c r="D18" t="b">
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -750,16 +750,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Automobiles</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-      <c r="D19" t="b">
-        <v>0</v>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -768,15 +768,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Automobiles</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="D20" t="b">
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -791,11 +791,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MARUTI</t>
-        </is>
-      </c>
-      <c r="D21" t="b">
-        <v>1</v>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -809,10 +809,10 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
-        </is>
-      </c>
-      <c r="D22" t="b">
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -827,10 +827,10 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
-        </is>
-      </c>
-      <c r="D23" t="b">
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -840,15 +840,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>Life Insurance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="D24" t="b">
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -858,15 +858,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>Life Insurance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
-        </is>
-      </c>
-      <c r="D25" t="b">
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -876,16 +876,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-      <c r="D26" t="b">
-        <v>0</v>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -894,15 +894,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -912,16 +912,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LICI</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>1</v>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -930,15 +930,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
-        </is>
-      </c>
-      <c r="D29" t="b">
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -948,15 +948,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
-        </is>
-      </c>
-      <c r="D30" t="b">
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -966,16 +966,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>Power &amp; Utilities</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
-        </is>
-      </c>
-      <c r="D31" t="b">
-        <v>0</v>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -984,16 +984,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Power &amp; Utilities</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
-        </is>
-      </c>
-      <c r="D32" t="b">
-        <v>1</v>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1002,15 +1002,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Power &amp; Utilities</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="D33" t="b">
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1020,15 +1020,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Power &amp; Utilities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BPCL</t>
-        </is>
-      </c>
-      <c r="D34" t="b">
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1038,15 +1038,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Power &amp; Utilities</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="D35" t="b">
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1056,16 +1056,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GAIL</t>
-        </is>
-      </c>
-      <c r="D36" t="b">
-        <v>0</v>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1074,16 +1074,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NTPC</t>
-        </is>
-      </c>
-      <c r="D37" t="b">
-        <v>1</v>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1092,15 +1092,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
-        </is>
-      </c>
-      <c r="D38" t="b">
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1110,15 +1110,15 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="D39" t="b">
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1128,16 +1128,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
-        </is>
-      </c>
-      <c r="D40" t="b">
-        <v>0</v>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1146,15 +1146,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NHPC</t>
-        </is>
-      </c>
-      <c r="D41" t="b">
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1164,15 +1164,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
-        </is>
-      </c>
-      <c r="D42" t="b">
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1182,15 +1182,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
-        </is>
-      </c>
-      <c r="D43" t="b">
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1200,16 +1200,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="D44" t="b">
-        <v>1</v>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1218,15 +1218,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
-        </is>
-      </c>
-      <c r="D45" t="b">
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1236,16 +1236,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Consumer Finance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
-        </is>
-      </c>
-      <c r="D46" t="b">
-        <v>0</v>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1254,15 +1254,15 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Consumer Finance</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
-        </is>
-      </c>
-      <c r="D47" t="b">
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1272,16 +1272,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Consumer Finance</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="D48" t="b">
-        <v>1</v>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1290,15 +1290,15 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Construction Materials</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="D49" t="b">
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1308,15 +1308,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="D50" t="b">
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1326,15 +1326,15 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DABUR</t>
-        </is>
-      </c>
-      <c r="D51" t="b">
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1344,15 +1344,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
-        </is>
-      </c>
-      <c r="D52" t="b">
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1362,15 +1362,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
-        </is>
-      </c>
-      <c r="D53" t="b">
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1380,15 +1380,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="D54" t="b">
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1398,16 +1398,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Consumer Finance</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
-        </is>
-      </c>
-      <c r="D55" t="b">
-        <v>1</v>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1416,15 +1416,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Consumer Finance</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
-        </is>
-      </c>
-      <c r="D56" t="b">
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1434,15 +1434,807 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Consumer Finance</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
-        </is>
-      </c>
-      <c r="D57" t="b">
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AMBUJACEM</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>JIOFIN</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>TATACAP</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>DMART</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ENRIN</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>TMCV</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
         <v>0</v>
       </c>
     </row>
